--- a/memory-bank/mvp-configuration-tables.xlsx
+++ b/memory-bank/mvp-configuration-tables.xlsx
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">砍击 6 伤害（50）；勒索 4 伤害并施加 1 层掠夺（30）；架盾获得 6 护甲（20）</t>
+          <t xml:space="preserve">砍击 6 伤害（50）；勒索 4 伤害并施加 1 层掠夺（30）；架盾获得 5 护甲（20）</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="0">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="E4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">劈砍 7 伤害（45）；断筋斩 8 伤害（35）；架势获得 7 护甲（20）</t>
+          <t xml:space="preserve">劈砍 7 伤害（45）；断筋斩 8 伤害（35）；架势获得 5 护甲（20）</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="0">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="E5" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">冲撞 10 伤害（50）；践踏全体 5 伤害（30）；蛰伏获得 6 护甲（20）</t>
+          <t xml:space="preserve">冲撞 10 伤害（50）；践踏全体 5 伤害（30）；蛰伏获得 5 护甲（20）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="0">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="D6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">72</t>
+          <t xml:space="preserve">62</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">重斩 10 伤害（40）；掠夺突袭 8 伤害、1 层围捕、1 层掠夺（30）；断筋斩 9 伤害（20）；号令获得 10 护甲（10）</t>
+          <t xml:space="preserve">重斩 10 伤害（40）；掠夺突袭 8 伤害、1 层围捕、1 层掠夺（30）；断筋斩 9 伤害（20）；号令获得 8 护甲（10）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="0">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">撞击 6 伤害（45）；孢子全体 3 伤害并施加 1 层疾病（35）；菌壳获得 5 护甲（20）</t>
+          <t xml:space="preserve">撞击 6 伤害（45）；孢子全体 3 伤害并施加 1 层疾病（35）；菌壳获得 4 护甲（20）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="0">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E9" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">箭射 8 伤害（45）；洗劫 5 伤害并施加 2 层掠夺（35）；伏守获得 8 护甲（20）</t>
+          <t xml:space="preserve">箭射 8 伤害（45）；洗劫 5 伤害并施加 2 层掠夺（35）；伏守获得 6 护甲（20）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="0">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">破骨冲撞 10 伤害（50）；横扫全体 5 伤害（30）；蓄势获得 7 护甲（20）</t>
+          <t xml:space="preserve">破骨冲撞 10 伤害（50）；横扫全体 5 伤害（30）；蓄势获得 5 护甲（20）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="0">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="D11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">80</t>
+          <t xml:space="preserve">68</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">树根重击 9 伤害（35）；孢子风暴全体 4 伤害并施加 1 层疾病（30）；缠枝 6 伤害并施加 2 层围捕（20）；树皮获得 12 护甲（15）</t>
+          <t xml:space="preserve">树根重击 9 伤害（35）；孢子风暴全体 4 伤害并施加 1 层疾病（30）；缠枝 6 伤害并施加 2 层围捕（20）；树皮获得 9 护甲（15）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="0">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B7" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">结算流血等开始时状态；抽 1 张；若手牌已达 5 张则不抽；能量重置为 3</t>
+          <t xml:space="preserve">结算流血等开始时状态；若手牌少于 4 张则补至 4 张，否则基础抽 1 张；若手牌已达上限 5 张则不抽；额外抽牌效果另行叠加；能量重置为 3</t>
         </is>
       </c>
     </row>
